--- a/events/Pau_2022_WC/Pau_2022_WC_start.xlsx
+++ b/events/Pau_2022_WC/Pau_2022_WC_start.xlsx
@@ -12431,7 +12431,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -31675,7 +31675,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
